--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
@@ -565,67 +565,67 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6918</v>
+        <v>10.6468</v>
       </c>
       <c r="E2" t="n">
-        <v>2.096200000000001</v>
+        <v>1.5648</v>
       </c>
       <c r="F2" t="n">
-        <v>8.595600000000001</v>
+        <v>9.082000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>6.8424</v>
+        <v>6.8644</v>
       </c>
       <c r="H2" t="n">
-        <v>7.184200000000001</v>
+        <v>7.146799999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3422</v>
+        <v>-0.2824</v>
       </c>
       <c r="J2" t="n">
-        <v>7.4054</v>
+        <v>7.234</v>
       </c>
       <c r="K2" t="n">
-        <v>6.2238</v>
+        <v>6.06</v>
       </c>
       <c r="L2" t="n">
-        <v>1.1816</v>
+        <v>1.174</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.3695999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9603999999999999</v>
+        <v>1.0866</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.5238</v>
+        <v>-1.4562</v>
       </c>
       <c r="P2" t="n">
-        <v>-8.768599999999999</v>
+        <v>-8.8604</v>
       </c>
       <c r="Q2" t="n">
-        <v>-14.7682</v>
+        <v>-14.9228</v>
       </c>
       <c r="R2" t="n">
-        <v>5.9996</v>
+        <v>6.0624</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8026</v>
+        <v>3.8606</v>
       </c>
       <c r="T2" t="n">
-        <v>3.7816</v>
+        <v>3.6424</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02099999999999991</v>
+        <v>0.2182000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>8.8156</v>
+        <v>8.782399999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>5.6774</v>
+        <v>5.6112</v>
       </c>
       <c r="X2" t="n">
-        <v>3.1382</v>
+        <v>3.171</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8278</v>
+        <v>6.8756</v>
       </c>
       <c r="E3" t="n">
-        <v>7.107799999999999</v>
+        <v>6.922199999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2799999999999998</v>
+        <v>-0.04659999999999997</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.130800000000001</v>
+        <v>-1.1018</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5813999999999999</v>
+        <v>-0.5580000000000003</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5497999999999998</v>
+        <v>-0.5436000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5834</v>
+        <v>1.5074</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1424</v>
+        <v>2.0868</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5590000000000002</v>
+        <v>-0.5792000000000002</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.7142</v>
+        <v>-2.6092</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.7236</v>
+        <v>-2.6448</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009399999999999992</v>
+        <v>0.03559999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>4.1536</v>
+        <v>4.197</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>4.1536</v>
+        <v>4.197</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7284</v>
+        <v>2.7128</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2936</v>
+        <v>2.2128</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4348</v>
+        <v>0.5002</v>
       </c>
       <c r="V3" t="n">
-        <v>1.077</v>
+        <v>1.0672</v>
       </c>
       <c r="W3" t="n">
-        <v>3.231</v>
+        <v>3.202</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.154</v>
+        <v>-2.1346</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0222</v>
+        <v>4.0298</v>
       </c>
       <c r="E4" t="n">
-        <v>2.224</v>
+        <v>2.017</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7982</v>
+        <v>2.0128</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3444</v>
+        <v>-1.347</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.6982</v>
+        <v>-2.6846</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3536</v>
+        <v>1.3376</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8215999999999997</v>
+        <v>0.7183999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.663</v>
+        <v>-1.7142</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4848</v>
+        <v>2.4326</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1662</v>
+        <v>-2.0654</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0352</v>
+        <v>-0.9703999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1312</v>
+        <v>-1.095</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4616</v>
+        <v>0.4664</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.7692</v>
+        <v>-2.798</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2306</v>
+        <v>3.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5358</v>
+        <v>3.5686</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5866</v>
+        <v>3.5476</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.05080000000000001</v>
+        <v>0.02120000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3694</v>
+        <v>1.342</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5848</v>
+        <v>0.5492</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7846</v>
+        <v>0.7927999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.852399999999999</v>
+        <v>2.8018</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9404</v>
+        <v>1.574000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9120000000000001</v>
+        <v>1.2278</v>
       </c>
       <c r="G5" t="n">
-        <v>8.119999999999999</v>
+        <v>8.1142</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.646</v>
+        <v>-2.5934</v>
       </c>
       <c r="I5" t="n">
-        <v>10.7662</v>
+        <v>10.7076</v>
       </c>
       <c r="J5" t="n">
-        <v>8.1326</v>
+        <v>7.994</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.2878</v>
+        <v>-3.3158</v>
       </c>
       <c r="L5" t="n">
-        <v>11.4204</v>
+        <v>11.3098</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01260000000000006</v>
+        <v>0.1202000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6418</v>
+        <v>0.7223999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6541999999999999</v>
+        <v>-0.6022000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.2304</v>
+        <v>-3.2642</v>
       </c>
       <c r="Q5" t="n">
-        <v>-7.8456</v>
+        <v>-7.9278</v>
       </c>
       <c r="R5" t="n">
-        <v>4.6152</v>
+        <v>4.6634</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1754</v>
+        <v>-0.1881999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2839999999999999</v>
+        <v>0.1656</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4594</v>
+        <v>-0.3538</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8616</v>
+        <v>-1.86</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3694</v>
+        <v>1.3418</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.231</v>
+        <v>-3.202</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4320000000000004</v>
+        <v>-0.3936000000000002</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7244</v>
+        <v>-1.8474</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2922</v>
+        <v>1.4538</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5688</v>
+        <v>-0.5577999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.1876</v>
+        <v>-4.1526</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6186</v>
+        <v>3.5948</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6936</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.845</v>
+        <v>-4.8508</v>
       </c>
       <c r="L6" t="n">
-        <v>4.151400000000001</v>
+        <v>4.112399999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1246</v>
+        <v>0.1806</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6574</v>
+        <v>0.698</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.533</v>
+        <v>-0.5171999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.923</v>
+        <v>0.9326000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3076</v>
+        <v>-2.3316</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2306</v>
+        <v>3.2644</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3678</v>
+        <v>1.3664</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2766</v>
+        <v>1.2226</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0912</v>
+        <v>0.1438</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.154</v>
+        <v>-2.1346</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.154</v>
+        <v>-2.1346</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9678000000000004</v>
+        <v>-1.0016</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.388999999999999</v>
+        <v>-1.7278</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4212</v>
+        <v>0.7262</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5354</v>
+        <v>3.5334</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3958</v>
+        <v>-1.3558</v>
       </c>
       <c r="I7" t="n">
-        <v>4.931</v>
+        <v>4.8892</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7576</v>
+        <v>3.6234</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6968</v>
+        <v>-1.7476</v>
       </c>
       <c r="L7" t="n">
-        <v>5.4546</v>
+        <v>5.371</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2224</v>
+        <v>-0.08999999999999997</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3014</v>
+        <v>0.3918</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5234</v>
+        <v>-0.4818</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.1536</v>
+        <v>-4.197</v>
       </c>
       <c r="Q7" t="n">
-        <v>-7.8458</v>
+        <v>-7.9278</v>
       </c>
       <c r="R7" t="n">
-        <v>3.692</v>
+        <v>3.7308</v>
       </c>
       <c r="S7" t="n">
-        <v>1.512</v>
+        <v>1.5218</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3296</v>
+        <v>1.2346</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1822</v>
+        <v>0.2874</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8616</v>
+        <v>-1.86</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3694</v>
+        <v>1.342</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.231</v>
+        <v>-3.202</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2446</v>
+        <v>-1.1998</v>
       </c>
       <c r="E8" t="n">
-        <v>5.251</v>
+        <v>4.9552</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.4954</v>
+        <v>-6.1548</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5926</v>
+        <v>2.562</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8972</v>
+        <v>2.891</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3048</v>
+        <v>-0.3291999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7454</v>
+        <v>2.5976</v>
       </c>
       <c r="K8" t="n">
-        <v>2.592</v>
+        <v>2.5054</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1532000000000002</v>
+        <v>0.09239999999999982</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.153</v>
+        <v>-0.03579999999999997</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3052</v>
+        <v>0.3856</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.458</v>
+        <v>-0.4214</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3844</v>
+        <v>1.399</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.7692</v>
+        <v>-2.798</v>
       </c>
       <c r="R8" t="n">
-        <v>4.1536</v>
+        <v>4.197</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2402</v>
+        <v>1.2434</v>
       </c>
       <c r="T8" t="n">
-        <v>2.0436</v>
+        <v>1.9534</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8031999999999999</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-6.462</v>
+        <v>-6.404</v>
       </c>
       <c r="W8" t="n">
-        <v>3.231</v>
+        <v>3.202</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.693</v>
+        <v>-9.606</v>
       </c>
     </row>
     <row r="9">
@@ -1111,40 +1111,40 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.128</v>
+        <v>-2.125</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6344</v>
+        <v>-1.6582</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4934</v>
+        <v>-0.4668</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.027</v>
+        <v>-2.008</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3636</v>
+        <v>-2.3448</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3366</v>
+        <v>0.3368</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6826</v>
+        <v>-1.6836</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6826</v>
+        <v>-1.6836</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3444</v>
+        <v>-0.3244</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.681</v>
+        <v>-0.6612</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3366</v>
+        <v>0.3368</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1008</v>
+        <v>-0.117</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0482</v>
+        <v>0.0254</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.149</v>
+        <v>-0.1424</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.456</v>
+        <v>-5.3598</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.6638</v>
+        <v>-10.8756</v>
       </c>
       <c r="F10" t="n">
-        <v>5.2078</v>
+        <v>5.5158</v>
       </c>
       <c r="G10" t="n">
-        <v>-9.661</v>
+        <v>-9.598800000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4114</v>
+        <v>-1.3314</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.2498</v>
+        <v>-8.2676</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.229199999999999</v>
+        <v>-9.2986</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3624000000000001</v>
+        <v>-0.3824</v>
       </c>
       <c r="L10" t="n">
-        <v>-8.8666</v>
+        <v>-8.916399999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4318</v>
+        <v>-0.3002</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0488</v>
+        <v>-0.9489999999999998</v>
       </c>
       <c r="O10" t="n">
-        <v>0.617</v>
+        <v>0.649</v>
       </c>
       <c r="P10" t="n">
-        <v>5.5382</v>
+        <v>5.596</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5.5382</v>
+        <v>5.596</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0406</v>
+        <v>-1.0824</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4346</v>
+        <v>-1.5768</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3938</v>
+        <v>0.4944</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2924</v>
+        <v>-0.2746</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2924</v>
+        <v>-0.2746</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.0754</v>
+        <v>-12.0656</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.2942</v>
+        <v>-13.7184</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2188</v>
+        <v>1.6526</v>
       </c>
       <c r="G11" t="n">
-        <v>-12.791</v>
+        <v>-12.726</v>
       </c>
       <c r="H11" t="n">
-        <v>-8.038399999999999</v>
+        <v>-7.9686</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.7526</v>
+        <v>-4.757400000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.310599999999999</v>
+        <v>-8.451599999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.9508</v>
+        <v>-5.03</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.3598</v>
+        <v>-3.4214</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.480399999999999</v>
+        <v>-4.2746</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.0876</v>
+        <v>-2.9388</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.393</v>
+        <v>-1.3358</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4614000000000003</v>
+        <v>-0.4661999999999997</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.9226</v>
+        <v>-6.995</v>
       </c>
       <c r="R11" t="n">
-        <v>6.4612</v>
+        <v>6.5288</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2692</v>
+        <v>-1.2824</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7998000000000001</v>
+        <v>-0.9556</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4694</v>
+        <v>-0.327</v>
       </c>
       <c r="V11" t="n">
-        <v>2.4464</v>
+        <v>2.4092</v>
       </c>
       <c r="W11" t="n">
-        <v>2.7388</v>
+        <v>2.6838</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2924</v>
+        <v>-0.2746</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.669</v>
+        <v>-18.7332</v>
       </c>
       <c r="E12" t="n">
-        <v>-16.9988</v>
+        <v>-17.3896</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6702</v>
+        <v>-1.3438</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.2738</v>
+        <v>-10.2092</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.824</v>
+        <v>-5.736</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.4496</v>
+        <v>-4.4732</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.253</v>
+        <v>-5.3786</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3922</v>
+        <v>-1.4472</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.8608</v>
+        <v>-3.9314</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.0206</v>
+        <v>-4.8306</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.431800000000001</v>
+        <v>-4.288600000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5888</v>
+        <v>-0.542</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.9226</v>
+        <v>-6.995</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.5378</v>
+        <v>-11.6584</v>
       </c>
       <c r="R12" t="n">
-        <v>4.6152</v>
+        <v>4.6632</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9805999999999999</v>
+        <v>-1.0108</v>
       </c>
       <c r="T12" t="n">
-        <v>0.284</v>
+        <v>0.1656</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2648</v>
+        <v>-1.1766</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4922</v>
+        <v>-0.5182</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.4922</v>
+        <v>-0.5182</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.1376</v>
+        <v>-20.0902</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.2138</v>
+        <v>-18.6652</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9238</v>
+        <v>-1.425</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.4868</v>
+        <v>-13.4168</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.726800000000001</v>
+        <v>-9.643000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.7598</v>
+        <v>-3.7734</v>
       </c>
       <c r="J13" t="n">
-        <v>-11.3622</v>
+        <v>-11.4992</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.648999999999999</v>
+        <v>-7.7146</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.7132</v>
+        <v>-3.7846</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.1246</v>
+        <v>-1.9176</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.078</v>
+        <v>-1.9286</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.04680000000000001</v>
+        <v>0.01119999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.0766</v>
+        <v>-5.1296</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.1532</v>
+        <v>-10.2594</v>
       </c>
       <c r="R13" t="n">
-        <v>5.0766</v>
+        <v>5.1296</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.774</v>
+        <v>-1.7874</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0066</v>
+        <v>-1.176</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7674000000000001</v>
+        <v>-0.6116000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1998</v>
+        <v>0.2435999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>4.308</v>
+        <v>4.2692</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.1082</v>
+        <v>-4.025600000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-36.7162</v>
+        <v>-36.6148</v>
       </c>
       <c r="E14" t="n">
-        <v>-45.299</v>
+        <v>-48.849</v>
       </c>
       <c r="F14" t="n">
-        <v>8.583000000000002</v>
+        <v>12.234</v>
       </c>
       <c r="G14" t="n">
-        <v>-30.1932</v>
+        <v>-29.8914</v>
       </c>
       <c r="H14" t="n">
-        <v>-28.7918</v>
+        <v>-28.3304</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4026</v>
+        <v>-1.560800000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.0852</v>
+        <v>-13.3752</v>
       </c>
       <c r="K14" t="n">
-        <v>-16.5714</v>
+        <v>-17.234</v>
       </c>
       <c r="L14" t="n">
-        <v>4.486600000000003</v>
+        <v>3.859199999999997</v>
       </c>
       <c r="M14" t="n">
-        <v>-18.1086</v>
+        <v>-16.5166</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.2198</v>
+        <v>-11.097</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.889199999999999</v>
+        <v>-5.419</v>
       </c>
       <c r="P14" t="n">
-        <v>-16.1524</v>
+        <v>-16.3214</v>
       </c>
       <c r="Q14" t="n">
-        <v>-66.9192</v>
+        <v>-67.61879999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>50.7664</v>
+        <v>51.297</v>
       </c>
       <c r="S14" t="n">
-        <v>8.8462</v>
+        <v>8.805400000000004</v>
       </c>
       <c r="T14" t="n">
-        <v>11.6868</v>
+        <v>10.4616</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.841</v>
+        <v>-1.6564</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7844000000000002</v>
+        <v>0.7929999999999983</v>
       </c>
       <c r="W14" t="n">
-        <v>22.0176</v>
+        <v>21.683</v>
       </c>
       <c r="X14" t="n">
-        <v>-21.2332</v>
+        <v>-20.8902</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6468</v>
+        <v>5.152</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5648</v>
+        <v>0.9338000000000002</v>
       </c>
       <c r="F2" t="n">
-        <v>9.082000000000001</v>
+        <v>4.2182</v>
       </c>
       <c r="G2" t="n">
-        <v>6.8644</v>
+        <v>3.1739</v>
       </c>
       <c r="H2" t="n">
-        <v>7.146799999999999</v>
+        <v>3.5171</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2824</v>
+        <v>-0.3432</v>
       </c>
       <c r="J2" t="n">
-        <v>7.234</v>
+        <v>3.8452</v>
       </c>
       <c r="K2" t="n">
-        <v>6.06</v>
+        <v>3.2524</v>
       </c>
       <c r="L2" t="n">
-        <v>1.174</v>
+        <v>0.5928</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3695999999999999</v>
+        <v>-0.6713</v>
       </c>
       <c r="N2" t="n">
-        <v>1.0866</v>
+        <v>0.2647</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4562</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>-8.8604</v>
+        <v>-4.3604</v>
       </c>
       <c r="Q2" t="n">
-        <v>-14.9228</v>
+        <v>-7.3439</v>
       </c>
       <c r="R2" t="n">
-        <v>6.0624</v>
+        <v>2.9835</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8606</v>
+        <v>1.922</v>
       </c>
       <c r="T2" t="n">
-        <v>3.6424</v>
+        <v>1.5765</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2182000000000001</v>
+        <v>0.3456</v>
       </c>
       <c r="V2" t="n">
-        <v>8.782399999999999</v>
+        <v>4.4164</v>
       </c>
       <c r="W2" t="n">
-        <v>5.6112</v>
+        <v>2.8559</v>
       </c>
       <c r="X2" t="n">
-        <v>3.171</v>
+        <v>1.5606</v>
       </c>
     </row>
     <row r="3">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8756</v>
+        <v>3.289</v>
       </c>
       <c r="E3" t="n">
-        <v>6.922199999999999</v>
+        <v>3.4946</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.04659999999999997</v>
+        <v>-0.2056</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.1018</v>
+        <v>-0.5992999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5580000000000003</v>
+        <v>-0.3163000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5436000000000001</v>
+        <v>-0.2830000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5074</v>
+        <v>0.9093</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0868</v>
+        <v>1.1183</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5792000000000002</v>
+        <v>-0.2089999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.6092</v>
+        <v>-1.5085</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.6448</v>
+        <v>-1.4346</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03559999999999999</v>
+        <v>-0.074</v>
       </c>
       <c r="P3" t="n">
-        <v>4.197</v>
+        <v>2.0655</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>4.197</v>
+        <v>2.0655</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7128</v>
+        <v>1.2818</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2128</v>
+        <v>0.9622999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5002</v>
+        <v>0.3195</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0672</v>
+        <v>0.541</v>
       </c>
       <c r="W3" t="n">
-        <v>3.202</v>
+        <v>1.623</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1346</v>
+        <v>-1.082</v>
       </c>
     </row>
     <row r="4">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0298</v>
+        <v>2.0531</v>
       </c>
       <c r="E4" t="n">
-        <v>2.017</v>
+        <v>1.2116</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0128</v>
+        <v>0.8414999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.347</v>
+        <v>-0.6194999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.6846</v>
+        <v>-1.32</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3376</v>
+        <v>0.7004999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7183999999999999</v>
+        <v>0.6335000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.7142</v>
+        <v>-0.7202999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4326</v>
+        <v>1.3538</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0654</v>
+        <v>-1.2529</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9703999999999999</v>
+        <v>-0.5995999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.095</v>
+        <v>-0.6532</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4664</v>
+        <v>0.2295</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.798</v>
+        <v>-1.377</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2644</v>
+        <v>1.6065</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5686</v>
+        <v>1.7512</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5476</v>
+        <v>1.6534</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02120000000000001</v>
+        <v>0.0978</v>
       </c>
       <c r="V4" t="n">
-        <v>1.342</v>
+        <v>0.6918</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5492</v>
+        <v>0.3017</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.3901</v>
       </c>
     </row>
     <row r="5">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8018</v>
+        <v>1.366099999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.574000000000001</v>
+        <v>1.0234</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2278</v>
+        <v>0.3425999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>8.1142</v>
+        <v>4.009300000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.5934</v>
+        <v>-1.3563</v>
       </c>
       <c r="I5" t="n">
-        <v>10.7076</v>
+        <v>5.3656</v>
       </c>
       <c r="J5" t="n">
-        <v>7.994</v>
+        <v>4.2982</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.3158</v>
+        <v>-1.5387</v>
       </c>
       <c r="L5" t="n">
-        <v>11.3098</v>
+        <v>5.8369</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1202000000000001</v>
+        <v>-0.2889</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7223999999999999</v>
+        <v>0.1824</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6022000000000001</v>
+        <v>-0.4712</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.2642</v>
+        <v>-1.6065</v>
       </c>
       <c r="Q5" t="n">
-        <v>-7.9278</v>
+        <v>-3.9014</v>
       </c>
       <c r="R5" t="n">
-        <v>4.6634</v>
+        <v>2.295</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1881999999999999</v>
+        <v>-0.1056</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1656</v>
+        <v>-0.06520000000000004</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3538</v>
+        <v>-0.04039999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.86</v>
+        <v>-0.9311</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3418</v>
+        <v>0.6919</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.202</v>
+        <v>-1.623</v>
       </c>
     </row>
     <row r="6">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3936000000000002</v>
+        <v>-0.2244999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8474</v>
+        <v>-0.8316999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4538</v>
+        <v>0.6073</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5577999999999999</v>
+        <v>-0.2546999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.1526</v>
+        <v>-2.0702</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5948</v>
+        <v>1.8155</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-0.2044999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.8508</v>
+        <v>-2.323</v>
       </c>
       <c r="L6" t="n">
-        <v>4.112399999999999</v>
+        <v>2.1186</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1806</v>
+        <v>-0.05019999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.698</v>
+        <v>0.2528</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5171999999999999</v>
+        <v>-0.303</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9326000000000001</v>
+        <v>0.459</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3316</v>
+        <v>-1.1475</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2644</v>
+        <v>1.6065</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3664</v>
+        <v>0.6533</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2226</v>
+        <v>0.5203000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1438</v>
+        <v>0.133</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1346</v>
+        <v>-1.082</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1346</v>
+        <v>-1.082</v>
       </c>
     </row>
     <row r="7">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0016</v>
+        <v>-0.4864000000000002</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7278</v>
+        <v>-0.5913999999999997</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7262</v>
+        <v>0.1049</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5334</v>
+        <v>1.7682</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3558</v>
+        <v>-0.7343</v>
       </c>
       <c r="I7" t="n">
-        <v>4.8892</v>
+        <v>2.5025</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6234</v>
+        <v>2.1422</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7476</v>
+        <v>-0.7373999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>5.371</v>
+        <v>2.8796</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08999999999999997</v>
+        <v>-0.374</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3918</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4818</v>
+        <v>-0.3770000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.197</v>
+        <v>-2.0654</v>
       </c>
       <c r="Q7" t="n">
-        <v>-7.9278</v>
+        <v>-3.9014</v>
       </c>
       <c r="R7" t="n">
-        <v>3.7308</v>
+        <v>1.836</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5218</v>
+        <v>0.742</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2346</v>
+        <v>0.476</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2874</v>
+        <v>0.266</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.86</v>
+        <v>-0.9312</v>
       </c>
       <c r="W7" t="n">
-        <v>1.342</v>
+        <v>0.6919000000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.202</v>
+        <v>-1.623</v>
       </c>
     </row>
     <row r="8">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1998</v>
+        <v>-0.6273</v>
       </c>
       <c r="E8" t="n">
-        <v>4.9552</v>
+        <v>2.7124</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.1548</v>
+        <v>-3.3397</v>
       </c>
       <c r="G8" t="n">
-        <v>2.562</v>
+        <v>1.3304</v>
       </c>
       <c r="H8" t="n">
-        <v>2.891</v>
+        <v>1.4046</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3291999999999999</v>
+        <v>-0.07430000000000014</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5976</v>
+        <v>1.6395</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5054</v>
+        <v>1.384</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09239999999999982</v>
+        <v>0.2556</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03579999999999997</v>
+        <v>-0.3092</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3856</v>
+        <v>0.0207</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4214</v>
+        <v>-0.3299</v>
       </c>
       <c r="P8" t="n">
-        <v>1.399</v>
+        <v>0.6885</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.798</v>
+        <v>-1.377</v>
       </c>
       <c r="R8" t="n">
-        <v>4.197</v>
+        <v>2.0655</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2434</v>
+        <v>0.5998</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9534</v>
+        <v>0.8267</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7102000000000001</v>
+        <v>-0.2269</v>
       </c>
       <c r="V8" t="n">
-        <v>-6.404</v>
+        <v>-3.246</v>
       </c>
       <c r="W8" t="n">
-        <v>3.202</v>
+        <v>1.623</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.606</v>
+        <v>-4.869</v>
       </c>
     </row>
     <row r="9">
@@ -1108,43 +1108,43 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.125</v>
+        <v>-1.081</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6582</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4668</v>
+        <v>-0.2569</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.008</v>
+        <v>-1.0054</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.3448</v>
+        <v>-1.1671</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3368</v>
+        <v>0.1617</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6836</v>
+        <v>-0.8084</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.6836</v>
+        <v>-0.8084</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3244</v>
+        <v>-0.1969</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6612</v>
+        <v>-0.3586</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3368</v>
+        <v>0.1617</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.117</v>
+        <v>-0.0756</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0254</v>
+        <v>-0.0156</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1424</v>
+        <v>-0.06</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.3598</v>
+        <v>-2.6961</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.8756</v>
+        <v>-5.1999</v>
       </c>
       <c r="F10" t="n">
-        <v>5.5158</v>
+        <v>2.5039</v>
       </c>
       <c r="G10" t="n">
-        <v>-9.598800000000001</v>
+        <v>-4.7293</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3314</v>
+        <v>-0.8048</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.2676</v>
+        <v>-3.9245</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.2986</v>
+        <v>-4.2702</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3824</v>
+        <v>-0.1434</v>
       </c>
       <c r="L10" t="n">
-        <v>-8.916399999999999</v>
+        <v>-4.1268</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3002</v>
+        <v>-0.459</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9489999999999998</v>
+        <v>-0.6614</v>
       </c>
       <c r="O10" t="n">
-        <v>0.649</v>
+        <v>0.2023</v>
       </c>
       <c r="P10" t="n">
-        <v>5.596</v>
+        <v>2.754</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5.596</v>
+        <v>2.754</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0824</v>
+        <v>-0.5698</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5768</v>
+        <v>-0.9298</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4944</v>
+        <v>0.3598</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2746</v>
+        <v>-0.1509</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2746</v>
+        <v>-0.1509</v>
       </c>
     </row>
     <row r="11">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.0656</v>
+        <v>-5.8835</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.7184</v>
+        <v>-6.4012</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6526</v>
+        <v>0.5176000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-12.726</v>
+        <v>-6.2558</v>
       </c>
       <c r="H11" t="n">
-        <v>-7.9686</v>
+        <v>-3.9787</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.757400000000001</v>
+        <v>-2.2771</v>
       </c>
       <c r="J11" t="n">
-        <v>-8.451599999999999</v>
+        <v>-3.6944</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.03</v>
+        <v>-2.259</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.4214</v>
+        <v>-1.4354</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.2746</v>
+        <v>-2.5614</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.9388</v>
+        <v>-1.7197</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3358</v>
+        <v>-0.8417</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4661999999999997</v>
+        <v>-0.2295</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.995</v>
+        <v>-3.4424</v>
       </c>
       <c r="R11" t="n">
-        <v>6.5288</v>
+        <v>3.213</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2824</v>
+        <v>-0.6311</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9556</v>
+        <v>-0.6481</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.327</v>
+        <v>0.01690000000000003</v>
       </c>
       <c r="V11" t="n">
-        <v>2.4092</v>
+        <v>1.2329</v>
       </c>
       <c r="W11" t="n">
-        <v>2.6838</v>
+        <v>1.3838</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2746</v>
+        <v>-0.1509</v>
       </c>
     </row>
     <row r="12">
@@ -1342,67 +1342,67 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.7332</v>
+        <v>-9.219899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-17.3896</v>
+        <v>-8.2768</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3438</v>
+        <v>-0.9431</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.2092</v>
+        <v>-5.0167</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.736</v>
+        <v>-2.9415</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.4732</v>
+        <v>-2.0752</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.3786</v>
+        <v>-2.235</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4472</v>
+        <v>-0.5839</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.9314</v>
+        <v>-1.6511</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.8306</v>
+        <v>-2.7817</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.288600000000001</v>
+        <v>-2.3576</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.542</v>
+        <v>-0.4241</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.995</v>
+        <v>-3.4424</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.6584</v>
+        <v>-5.7374</v>
       </c>
       <c r="R12" t="n">
-        <v>4.6632</v>
+        <v>2.295</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0108</v>
+        <v>-0.5215000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1656</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1766</v>
+        <v>-0.4564</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5182</v>
+        <v>-0.2393</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.5182</v>
+        <v>-0.2393</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.0902</v>
+        <v>-9.895199999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.6652</v>
+        <v>-8.811399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.425</v>
+        <v>-1.0838</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.4168</v>
+        <v>-6.5855</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.643000000000001</v>
+        <v>-4.8136</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.7734</v>
+        <v>-1.7719</v>
       </c>
       <c r="J13" t="n">
-        <v>-11.4992</v>
+        <v>-5.1559</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.7146</v>
+        <v>-3.579</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.7846</v>
+        <v>-1.5769</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9176</v>
+        <v>-1.4296</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9286</v>
+        <v>-1.2345</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01119999999999999</v>
+        <v>-0.195</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.1296</v>
+        <v>-2.5245</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.2594</v>
+        <v>-5.0489</v>
       </c>
       <c r="R13" t="n">
-        <v>5.1296</v>
+        <v>2.5245</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7874</v>
+        <v>-0.8736999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.176</v>
+        <v>-0.7706000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6116000000000001</v>
+        <v>-0.103</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2435999999999999</v>
+        <v>0.08839999999999998</v>
       </c>
       <c r="W13" t="n">
-        <v>4.2692</v>
+        <v>2.164</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.025600000000001</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="14">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-36.6148</v>
+        <v>-18.2537</v>
       </c>
       <c r="E14" t="n">
-        <v>-48.849</v>
+        <v>-21.5607</v>
       </c>
       <c r="F14" t="n">
-        <v>12.234</v>
+        <v>3.306899999999998</v>
       </c>
       <c r="G14" t="n">
-        <v>-29.8914</v>
+        <v>-14.7844</v>
       </c>
       <c r="H14" t="n">
-        <v>-28.3304</v>
+        <v>-14.5811</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.560800000000002</v>
+        <v>-0.203400000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>-13.3752</v>
+        <v>-2.900500000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-17.234</v>
+        <v>-6.9384</v>
       </c>
       <c r="L14" t="n">
-        <v>3.859199999999997</v>
+        <v>4.0381</v>
       </c>
       <c r="M14" t="n">
-        <v>-16.5166</v>
+        <v>-11.8836</v>
       </c>
       <c r="N14" t="n">
-        <v>-11.097</v>
+        <v>-7.6424</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.419</v>
+        <v>-4.2411</v>
       </c>
       <c r="P14" t="n">
-        <v>-16.3214</v>
+        <v>-8.0322</v>
       </c>
       <c r="Q14" t="n">
-        <v>-67.61879999999999</v>
+        <v>-33.2769</v>
       </c>
       <c r="R14" t="n">
-        <v>51.297</v>
+        <v>25.245</v>
       </c>
       <c r="S14" t="n">
-        <v>8.805400000000004</v>
+        <v>4.172800000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>10.4616</v>
+        <v>3.5207</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6564</v>
+        <v>0.6519</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7929999999999983</v>
+        <v>0.3899999999999997</v>
       </c>
       <c r="W14" t="n">
-        <v>21.683</v>
+        <v>11.0959</v>
       </c>
       <c r="X14" t="n">
-        <v>-20.8902</v>
+        <v>-10.7058</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>5.152</v>
+        <v>5.1001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9338000000000002</v>
+        <v>0.4283000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2182</v>
+        <v>4.6717</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1739</v>
+        <v>3.1822</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5171</v>
+        <v>3.478</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3432</v>
+        <v>-0.2958</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8452</v>
+        <v>3.6913</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2524</v>
+        <v>3.1057</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5928</v>
+        <v>0.5856</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6713</v>
+        <v>-0.5091</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2647</v>
+        <v>0.3724</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.8815</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.3604</v>
+        <v>-4.4454</v>
       </c>
       <c r="Q2" t="n">
-        <v>-7.3439</v>
+        <v>-7.4871</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9835</v>
+        <v>3.0416</v>
       </c>
       <c r="S2" t="n">
-        <v>1.922</v>
+        <v>1.9777</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5765</v>
+        <v>1.4296</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3456</v>
+        <v>0.5481</v>
       </c>
       <c r="V2" t="n">
-        <v>4.4164</v>
+        <v>4.3856</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8559</v>
+        <v>2.7946</v>
       </c>
       <c r="X2" t="n">
-        <v>1.5606</v>
+        <v>1.591</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.289</v>
+        <v>3.3273</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4946</v>
+        <v>3.3171</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2056</v>
+        <v>0.01029999999999998</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5992999999999999</v>
+        <v>-0.5733999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3163000000000001</v>
+        <v>-0.2958000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2830000000000001</v>
+        <v>-0.2775999999999998</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9093</v>
+        <v>0.8439000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1183</v>
+        <v>1.0684</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2089999999999999</v>
+        <v>-0.2244999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5085</v>
+        <v>-1.4173</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4346</v>
+        <v>-1.3641</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.074</v>
+        <v>-0.05329999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2818</v>
+        <v>1.263</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9622999999999999</v>
+        <v>0.8769</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3195</v>
+        <v>0.386</v>
       </c>
       <c r="V3" t="n">
-        <v>0.541</v>
+        <v>0.532</v>
       </c>
       <c r="W3" t="n">
-        <v>1.623</v>
+        <v>1.5962</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0531</v>
+        <v>2.0625</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2116</v>
+        <v>1.0221</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8414999999999999</v>
+        <v>1.0404</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6194999999999999</v>
+        <v>-0.6191</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.32</v>
+        <v>-1.3057</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7004999999999999</v>
+        <v>0.6865999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6335000000000001</v>
+        <v>0.5476000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7202999999999999</v>
+        <v>-0.7628</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3538</v>
+        <v>1.3104</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2529</v>
+        <v>-1.1667</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5995999999999999</v>
+        <v>-0.5429999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6532</v>
+        <v>-0.6238</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.377</v>
+        <v>-1.4039</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7512</v>
+        <v>1.7813</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6534</v>
+        <v>1.6097</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0978</v>
+        <v>0.1716</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6918</v>
+        <v>0.6664</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3017</v>
+        <v>0.2686</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3901</v>
+        <v>0.3978</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.366099999999999</v>
+        <v>1.3153</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0234</v>
+        <v>0.6812999999999998</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3425999999999999</v>
+        <v>0.634</v>
       </c>
       <c r="G5" t="n">
-        <v>4.009300000000001</v>
+        <v>4.001399999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3563</v>
+        <v>-1.3085</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3656</v>
+        <v>5.3098</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2982</v>
+        <v>4.1796</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.5387</v>
+        <v>-1.5597</v>
       </c>
       <c r="L5" t="n">
-        <v>5.8369</v>
+        <v>5.7393</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2889</v>
+        <v>-0.1782</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1824</v>
+        <v>0.2513</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4712</v>
+        <v>-0.4295</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6065</v>
+        <v>-1.6378</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9014</v>
+        <v>-3.9775</v>
       </c>
       <c r="R5" t="n">
-        <v>2.295</v>
+        <v>2.3397</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1056</v>
+        <v>-0.1184000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06520000000000004</v>
+        <v>-0.1870999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.04039999999999999</v>
+        <v>0.0687</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9311</v>
+        <v>-0.9298000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6919</v>
+        <v>0.6664</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.623</v>
+        <v>-1.5962</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2244999999999999</v>
+        <v>-0.1886000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8316999999999999</v>
+        <v>-0.9459000000000002</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6073</v>
+        <v>0.7573000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2546999999999999</v>
+        <v>-0.2428000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0702</v>
+        <v>-2.0363</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8155</v>
+        <v>1.7935</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2044999999999999</v>
+        <v>-0.2395999999999998</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.323</v>
+        <v>-2.3235</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1186</v>
+        <v>2.0839</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.05019999999999999</v>
+        <v>-0.003200000000000036</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2528</v>
+        <v>0.2872</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.303</v>
+        <v>-0.2904</v>
       </c>
       <c r="P6" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6065</v>
+        <v>1.6378</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6533</v>
+        <v>0.6504</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5203000000000001</v>
+        <v>0.4635</v>
       </c>
       <c r="U6" t="n">
-        <v>0.133</v>
+        <v>0.1868</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4864000000000002</v>
+        <v>-0.5185</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5913999999999997</v>
+        <v>-0.9049</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1049</v>
+        <v>0.3864</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7682</v>
+        <v>1.7664</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7343</v>
+        <v>-0.6987</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5025</v>
+        <v>2.4651</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1422</v>
+        <v>2.0293</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7373999999999999</v>
+        <v>-0.7794</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8796</v>
+        <v>2.8087</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.374</v>
+        <v>-0.2629</v>
       </c>
       <c r="N7" t="n">
-        <v>0.003000000000000003</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3770000000000001</v>
+        <v>-0.3435999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0654</v>
+        <v>-2.1058</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.9014</v>
+        <v>-3.9776</v>
       </c>
       <c r="R7" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S7" t="n">
-        <v>0.742</v>
+        <v>0.7507</v>
       </c>
       <c r="T7" t="n">
-        <v>0.476</v>
+        <v>0.3769999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.266</v>
+        <v>0.3736</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9312</v>
+        <v>-0.9298</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6919000000000001</v>
+        <v>0.6664</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.623</v>
+        <v>-1.5962</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6273</v>
+        <v>-0.5856</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7124</v>
+        <v>2.4386</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3397</v>
+        <v>-3.0242</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3304</v>
+        <v>1.3032</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4046</v>
+        <v>1.3964</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.07430000000000014</v>
+        <v>-0.09320000000000006</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6395</v>
+        <v>1.5142</v>
       </c>
       <c r="K8" t="n">
-        <v>1.384</v>
+        <v>1.3067</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2556</v>
+        <v>0.2074999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3092</v>
+        <v>-0.2109</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0207</v>
+        <v>0.0897</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3299</v>
+        <v>-0.3007</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.377</v>
+        <v>-1.4039</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0655</v>
+        <v>2.1058</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5998</v>
+        <v>0.6016</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8267</v>
+        <v>0.7321</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2269</v>
+        <v>-0.1304999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.246</v>
+        <v>-3.1923</v>
       </c>
       <c r="W8" t="n">
-        <v>1.623</v>
+        <v>1.5962</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.869</v>
+        <v>-4.7885</v>
       </c>
     </row>
     <row r="9">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.081</v>
+        <v>-1.0792</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.8468</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2569</v>
+        <v>-0.2324</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0054</v>
+        <v>-0.9872</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1671</v>
+        <v>-1.1487</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1617</v>
+        <v>0.1615</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8084</v>
+        <v>-0.8077</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8084</v>
+        <v>-0.8077</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1969</v>
+        <v>-0.1795</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3586</v>
+        <v>-0.341</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1617</v>
+        <v>0.1615</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0756</v>
+        <v>-0.092</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0156</v>
+        <v>-0.0391</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.06</v>
+        <v>-0.0529</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6961</v>
+        <v>-2.6039</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.1999</v>
+        <v>-5.3925</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5039</v>
+        <v>2.7886</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.7293</v>
+        <v>-4.6657</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8048</v>
+        <v>-0.7346</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.9245</v>
+        <v>-3.9311</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.2702</v>
+        <v>-4.3182</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1434</v>
+        <v>-0.1602</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.1268</v>
+        <v>-4.157999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.459</v>
+        <v>-0.3475</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6614</v>
+        <v>-0.5744</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2023</v>
+        <v>0.2269</v>
       </c>
       <c r="P10" t="n">
-        <v>2.754</v>
+        <v>2.8077</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.754</v>
+        <v>2.8077</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5698</v>
+        <v>-0.6114999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9298</v>
+        <v>-1.0743</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3598</v>
+        <v>0.4628</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8835</v>
+        <v>-5.8667</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.4012</v>
+        <v>-6.7875</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5176000000000001</v>
+        <v>0.9208</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.2558</v>
+        <v>-6.1877</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.9787</v>
+        <v>-3.9111</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2771</v>
+        <v>-2.2766</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.6944</v>
+        <v>-3.8037</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.259</v>
+        <v>-2.3225</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4354</v>
+        <v>-1.4811</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5614</v>
+        <v>-2.3841</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7197</v>
+        <v>-1.5886</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8417</v>
+        <v>-0.7955</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2295</v>
+        <v>-0.234</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4424</v>
+        <v>-3.5096</v>
       </c>
       <c r="R11" t="n">
-        <v>3.213</v>
+        <v>3.2756</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6311</v>
+        <v>-0.6434</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6481</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01690000000000003</v>
+        <v>0.1635</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3838</v>
+        <v>1.3327</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.219899999999999</v>
+        <v>-9.2745</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.2768</v>
+        <v>-8.632999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9431</v>
+        <v>-0.6415000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.0167</v>
+        <v>-4.9499</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.9415</v>
+        <v>-2.8602</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0752</v>
+        <v>-2.0897</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.235</v>
+        <v>-2.3331</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5839</v>
+        <v>-0.6299</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.6511</v>
+        <v>-1.7032</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.7817</v>
+        <v>-2.6168</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.3576</v>
+        <v>-2.2302</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4241</v>
+        <v>-0.3865</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.4424</v>
+        <v>-3.5096</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.7374</v>
+        <v>-5.8493</v>
       </c>
       <c r="R12" t="n">
-        <v>2.295</v>
+        <v>2.3398</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5215000000000001</v>
+        <v>-0.5516</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.1871</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4564</v>
+        <v>-0.3645</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2393</v>
+        <v>-0.2634</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2393</v>
+        <v>-0.2634</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.895199999999999</v>
+        <v>-9.841799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.811399999999999</v>
+        <v>-9.221</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0838</v>
+        <v>-0.6208999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.5855</v>
+        <v>-6.5116</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.8136</v>
+        <v>-4.7322</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7719</v>
+        <v>-1.7793</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.1559</v>
+        <v>-5.2583</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.579</v>
+        <v>-3.6283</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.5769</v>
+        <v>-1.63</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4296</v>
+        <v>-1.2533</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2345</v>
+        <v>-1.104</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.195</v>
+        <v>-0.1494</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.5245</v>
+        <v>-2.5737</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.0489</v>
+        <v>-5.147399999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5245</v>
+        <v>2.5737</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8736999999999999</v>
+        <v>-0.8856999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7706000000000001</v>
+        <v>-0.9435</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.103</v>
+        <v>0.05779999999999996</v>
       </c>
       <c r="V13" t="n">
-        <v>0.08839999999999998</v>
+        <v>0.1292</v>
       </c>
       <c r="W13" t="n">
-        <v>2.164</v>
+        <v>2.1282</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.0757</v>
+        <v>-1.9991</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.2537</v>
+        <v>-18.1536</v>
       </c>
       <c r="E14" t="n">
-        <v>-21.5607</v>
+        <v>-24.8442</v>
       </c>
       <c r="F14" t="n">
-        <v>3.306899999999998</v>
+        <v>6.690499999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.7844</v>
+        <v>-14.4842</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.5811</v>
+        <v>-14.1574</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.203400000000002</v>
+        <v>-0.3267999999999993</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.900500000000001</v>
+        <v>-3.9547</v>
       </c>
       <c r="K14" t="n">
-        <v>-6.9384</v>
+        <v>-7.493200000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>4.0381</v>
+        <v>3.538600000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-11.8836</v>
+        <v>-10.5295</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.6424</v>
+        <v>-6.664</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.2411</v>
+        <v>-3.8658</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.0322</v>
+        <v>-8.1891</v>
       </c>
       <c r="Q14" t="n">
-        <v>-33.2769</v>
+        <v>-33.9262</v>
       </c>
       <c r="R14" t="n">
-        <v>25.245</v>
+        <v>25.737</v>
       </c>
       <c r="S14" t="n">
-        <v>4.172800000000001</v>
+        <v>4.122100000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5207</v>
+        <v>2.250700000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6519</v>
+        <v>1.871</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3899999999999997</v>
+        <v>0.3978999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>11.0959</v>
+        <v>10.7859</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.7058</v>
+        <v>-10.388</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1001</v>
+        <v>5.174799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4283000000000001</v>
+        <v>0.7077</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6717</v>
+        <v>4.4671</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1822</v>
+        <v>3.2405</v>
       </c>
       <c r="H2" t="n">
-        <v>3.478</v>
+        <v>3.5164</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2958</v>
+        <v>-0.2758</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6913</v>
+        <v>3.7316</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1057</v>
+        <v>3.1429</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5856</v>
+        <v>0.5886</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5091</v>
+        <v>-0.4911</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3724</v>
+        <v>0.3734</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8815</v>
+        <v>-0.8644999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.4454</v>
+        <v>-4.4093</v>
       </c>
       <c r="Q2" t="n">
-        <v>-7.4871</v>
+        <v>-7.4263</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0416</v>
+        <v>3.0169</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9777</v>
+        <v>1.9448</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4296</v>
+        <v>1.5818</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5481</v>
+        <v>0.3631</v>
       </c>
       <c r="V2" t="n">
-        <v>4.3856</v>
+        <v>4.3987</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7946</v>
+        <v>2.8206</v>
       </c>
       <c r="X2" t="n">
-        <v>1.591</v>
+        <v>1.5781</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3273</v>
+        <v>3.3399</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3171</v>
+        <v>3.42</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01029999999999998</v>
+        <v>-0.08009999999999995</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5733999999999999</v>
+        <v>-0.5777000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2958000000000001</v>
+        <v>-0.2995000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2775999999999998</v>
+        <v>-0.2782</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8439000000000001</v>
+        <v>0.8466</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0684</v>
+        <v>1.0812</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2244999999999999</v>
+        <v>-0.2346999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4173</v>
+        <v>-1.4243</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3641</v>
+        <v>-1.3807</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.05329999999999999</v>
+        <v>-0.0436</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1057</v>
+        <v>2.0886</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1057</v>
+        <v>2.0886</v>
       </c>
       <c r="S3" t="n">
-        <v>1.263</v>
+        <v>1.2931</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8769</v>
+        <v>0.9659</v>
       </c>
       <c r="U3" t="n">
-        <v>0.386</v>
+        <v>0.3273</v>
       </c>
       <c r="V3" t="n">
-        <v>0.532</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5962</v>
+        <v>1.6076</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0625</v>
+        <v>2.0472</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0221</v>
+        <v>1.0908</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0404</v>
+        <v>0.9563999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6191</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3057</v>
+        <v>-1.3202</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6865999999999999</v>
+        <v>0.6875</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5476000000000001</v>
+        <v>0.5339</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7628</v>
+        <v>-0.7698</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3104</v>
+        <v>1.3037</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1667</v>
+        <v>-1.1665</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5429999999999999</v>
+        <v>-0.5504</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6238</v>
+        <v>-0.6162</v>
       </c>
       <c r="P4" t="n">
-        <v>0.234</v>
+        <v>0.2321</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.4039</v>
+        <v>-1.3925</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7813</v>
+        <v>1.7706</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6097</v>
+        <v>1.6667</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1716</v>
+        <v>0.1039</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6664</v>
+        <v>0.6772</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2686</v>
+        <v>0.2827</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3978</v>
+        <v>0.3945</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3153</v>
+        <v>1.3557</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6812999999999998</v>
+        <v>0.8373999999999997</v>
       </c>
       <c r="F5" t="n">
-        <v>0.634</v>
+        <v>0.5183</v>
       </c>
       <c r="G5" t="n">
-        <v>4.001399999999999</v>
+        <v>4.0181</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3085</v>
+        <v>-1.3238</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3098</v>
+        <v>5.3419</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1796</v>
+        <v>4.1798</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.5597</v>
+        <v>-1.5759</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7393</v>
+        <v>5.7557</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1782</v>
+        <v>-0.1617</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2513</v>
+        <v>0.2521</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4295</v>
+        <v>-0.4137999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6378</v>
+        <v>-1.6245</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9775</v>
+        <v>-3.9452</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3397</v>
+        <v>2.3207</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1184000000000001</v>
+        <v>-0.1076</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1870999999999999</v>
+        <v>-0.07440000000000002</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0687</v>
+        <v>-0.03320000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9298000000000001</v>
+        <v>-0.9304000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6664</v>
+        <v>0.6772</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5962</v>
+        <v>-1.6076</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1886000000000001</v>
+        <v>-0.2042000000000002</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9459000000000002</v>
+        <v>-0.8970000000000002</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7573000000000001</v>
+        <v>0.6928</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2428000000000001</v>
+        <v>-0.2562</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0363</v>
+        <v>-2.0591</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7935</v>
+        <v>1.8029</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2395999999999998</v>
+        <v>-0.2581</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.3235</v>
+        <v>-2.3484</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0839</v>
+        <v>2.0903</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.003200000000000036</v>
+        <v>0.001900000000000013</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2872</v>
+        <v>0.2893</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2904</v>
+        <v>-0.2874</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4679</v>
+        <v>0.4641000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1699</v>
+        <v>-1.1604</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6378</v>
+        <v>1.6245</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6504</v>
+        <v>0.6595</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4635</v>
+        <v>0.5214</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1868</v>
+        <v>0.1381</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0641</v>
+        <v>-1.0717</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5185</v>
+        <v>-0.5020000000000002</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9049</v>
+        <v>-0.7756000000000003</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3864</v>
+        <v>0.2736</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7664</v>
+        <v>1.7672</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6987</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4651</v>
+        <v>2.4743</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0293</v>
+        <v>2.0187</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7794</v>
+        <v>-0.7866000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8087</v>
+        <v>2.8053</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2629</v>
+        <v>-0.2515</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0795</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3435999999999999</v>
+        <v>-0.3310999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1058</v>
+        <v>-2.0887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.9776</v>
+        <v>-3.9452</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8718</v>
+        <v>1.8566</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7507</v>
+        <v>0.7499</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3769999999999999</v>
+        <v>0.4737000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3736</v>
+        <v>0.2761</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9298</v>
+        <v>-0.9304</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6664</v>
+        <v>0.6772</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5962</v>
+        <v>-1.6076</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5856</v>
+        <v>-0.605</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4386</v>
+        <v>2.5523</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0242</v>
+        <v>-3.1573</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3032</v>
+        <v>1.308</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3964</v>
+        <v>1.4116</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09320000000000006</v>
+        <v>-0.1034999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5142</v>
+        <v>1.509</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3067</v>
+        <v>1.3228</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2074999999999999</v>
+        <v>0.1860999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2109</v>
+        <v>-0.2008</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0897</v>
+        <v>0.0888</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3007</v>
+        <v>-0.2897</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7019</v>
+        <v>0.6962</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.4039</v>
+        <v>-1.3925</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1058</v>
+        <v>2.0887</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6016</v>
+        <v>0.6059</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7321</v>
+        <v>0.8281999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1304999999999999</v>
+        <v>-0.2224</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.1923</v>
+        <v>-3.215100000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5962</v>
+        <v>1.6076</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.7885</v>
+        <v>-4.8227</v>
       </c>
     </row>
     <row r="9">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0792</v>
+        <v>-1.0758</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8468</v>
+        <v>-0.8338</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2324</v>
+        <v>-0.242</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9872</v>
+        <v>-0.9983</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1487</v>
+        <v>-1.1615</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1615</v>
+        <v>0.1633</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8077</v>
+        <v>-0.8164</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8077</v>
+        <v>-0.8164</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1795</v>
+        <v>-0.1819</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.341</v>
+        <v>-0.3452</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1615</v>
+        <v>0.1633</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.092</v>
+        <v>-0.0775</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0391</v>
+        <v>-0.0174</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0529</v>
+        <v>-0.0601</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6039</v>
+        <v>-2.6576</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.3925</v>
+        <v>-5.3303</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7886</v>
+        <v>2.6728</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.6657</v>
+        <v>-4.7228</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7346</v>
+        <v>-0.7444</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.9311</v>
+        <v>-3.9784</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.3182</v>
+        <v>-4.3814</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1602</v>
+        <v>-0.1614</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.157999999999999</v>
+        <v>-4.2199</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3475</v>
+        <v>-0.3413</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5744</v>
+        <v>-0.5829</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2269</v>
+        <v>0.2415</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8077</v>
+        <v>2.7849</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8077</v>
+        <v>2.7849</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6114999999999999</v>
+        <v>-0.5784</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0743</v>
+        <v>-0.9490000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4628</v>
+        <v>0.3706</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8667</v>
+        <v>-5.914</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.7875</v>
+        <v>-6.6582</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9208</v>
+        <v>0.7441999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.1877</v>
+        <v>-6.2567</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.9111</v>
+        <v>-3.9548</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2766</v>
+        <v>-2.3019</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.8037</v>
+        <v>-3.8659</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.3225</v>
+        <v>-2.3457</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4811</v>
+        <v>-1.5202</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3841</v>
+        <v>-2.3908</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5886</v>
+        <v>-1.6091</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7955</v>
+        <v>-0.7817</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.234</v>
+        <v>-0.2321</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.5096</v>
+        <v>-3.4811</v>
       </c>
       <c r="R11" t="n">
-        <v>3.2756</v>
+        <v>3.249</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6434</v>
+        <v>-0.6382</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.6656</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1635</v>
+        <v>0.02740000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1984</v>
+        <v>1.2131</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3327</v>
+        <v>1.3544</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1343</v>
+        <v>-0.1413</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.2745</v>
+        <v>-9.276399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.632999999999999</v>
+        <v>-8.512700000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6415000000000001</v>
+        <v>-0.7638</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.9499</v>
+        <v>-5.013400000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.8602</v>
+        <v>-2.893</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0897</v>
+        <v>-2.1204</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.3331</v>
+        <v>-2.3834</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6299</v>
+        <v>-0.6355</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.7032</v>
+        <v>-1.7479</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.6168</v>
+        <v>-2.63</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.2302</v>
+        <v>-2.2575</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3865</v>
+        <v>-0.3724999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.5096</v>
+        <v>-3.4811</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.8493</v>
+        <v>-5.8018</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3398</v>
+        <v>2.3208</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5516</v>
+        <v>-0.5287999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1871</v>
+        <v>-0.0743</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3645</v>
+        <v>-0.4544</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2634</v>
+        <v>-0.2532</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2634</v>
+        <v>-0.2532</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.841799999999999</v>
+        <v>-9.912100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.221</v>
+        <v>-9.092599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6208999999999999</v>
+        <v>-0.8195000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.5116</v>
+        <v>-6.588100000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.7322</v>
+        <v>-4.7852</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7793</v>
+        <v>-1.8029</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.2583</v>
+        <v>-5.3402</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.6283</v>
+        <v>-3.6659</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.63</v>
+        <v>-1.6743</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2533</v>
+        <v>-1.2479</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.104</v>
+        <v>-1.1193</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1494</v>
+        <v>-0.1286</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.5737</v>
+        <v>-2.5528</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.147399999999999</v>
+        <v>-5.1055</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5737</v>
+        <v>2.5528</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8856999999999999</v>
+        <v>-0.8831</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9435</v>
+        <v>-0.7904</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05779999999999996</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1292</v>
+        <v>0.1118</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1282</v>
+        <v>2.1434</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.9991</v>
+        <v>-2.0316</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.1536</v>
+        <v>-18.2295</v>
       </c>
       <c r="E14" t="n">
-        <v>-24.8442</v>
+        <v>-23.492</v>
       </c>
       <c r="F14" t="n">
-        <v>6.690499999999999</v>
+        <v>5.262500000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.4842</v>
+        <v>-14.712</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.1574</v>
+        <v>-14.3207</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3267999999999993</v>
+        <v>-0.3912000000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.9547</v>
+        <v>-4.2258</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.493200000000001</v>
+        <v>-7.558699999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>3.538600000000001</v>
+        <v>3.332700000000002</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.5295</v>
+        <v>-10.4859</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.664</v>
+        <v>-6.762</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.8658</v>
+        <v>-3.7243</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.1891</v>
+        <v>-8.122599999999998</v>
       </c>
       <c r="Q14" t="n">
-        <v>-33.9262</v>
+        <v>-33.6505</v>
       </c>
       <c r="R14" t="n">
-        <v>25.737</v>
+        <v>25.528</v>
       </c>
       <c r="S14" t="n">
-        <v>4.122100000000001</v>
+        <v>4.210199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.250700000000001</v>
+        <v>3.466600000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.871</v>
+        <v>0.7436000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3978999999999999</v>
+        <v>0.3945000000000003</v>
       </c>
       <c r="W14" t="n">
-        <v>10.7859</v>
+        <v>10.9175</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.388</v>
+        <v>-10.5229</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>5.174799999999999</v>
+        <v>5.2079</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7077</v>
+        <v>0.5813999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4671</v>
+        <v>4.6265</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2405</v>
+        <v>3.3057</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5164</v>
+        <v>3.5234</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2758</v>
+        <v>-0.2177</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7316</v>
+        <v>3.6481</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1429</v>
+        <v>3.0622</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5886</v>
+        <v>0.586</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4911</v>
+        <v>-0.3425</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3734</v>
+        <v>0.4611</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8644999999999999</v>
+        <v>-0.8036</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.4093</v>
+        <v>-4.4415</v>
       </c>
       <c r="Q2" t="n">
-        <v>-7.4263</v>
+        <v>-7.480499999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0169</v>
+        <v>3.039</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9448</v>
+        <v>1.9567</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5818</v>
+        <v>1.6163</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3631</v>
+        <v>0.3404</v>
       </c>
       <c r="V2" t="n">
-        <v>4.3987</v>
+        <v>4.387</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8206</v>
+        <v>2.7974</v>
       </c>
       <c r="X2" t="n">
-        <v>1.5781</v>
+        <v>1.5896</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3399</v>
+        <v>3.3834</v>
       </c>
       <c r="E3" t="n">
-        <v>3.42</v>
+        <v>3.3805</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.08009999999999995</v>
+        <v>0.002800000000000025</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5777000000000001</v>
+        <v>-0.5611999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2995000000000001</v>
+        <v>-0.2866</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2782</v>
+        <v>-0.2746</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8466</v>
+        <v>0.7966999999999997</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0812</v>
+        <v>1.054</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2346999999999999</v>
+        <v>-0.2573000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4243</v>
+        <v>-1.358</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3807</v>
+        <v>-1.3406</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0436</v>
+        <v>-0.0173</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0886</v>
+        <v>2.1039</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0886</v>
+        <v>2.1039</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2931</v>
+        <v>1.3083</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9659</v>
+        <v>0.9863999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3273</v>
+        <v>0.3219</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.5324</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6076</v>
+        <v>1.5974</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0717</v>
+        <v>-1.0649</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0472</v>
+        <v>2.0394</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0908</v>
+        <v>1.0073</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9563999999999999</v>
+        <v>1.0321</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.6459000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3202</v>
+        <v>-1.3231</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6875</v>
+        <v>0.6772999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5339</v>
+        <v>0.4511999999999998</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7698</v>
+        <v>-0.8110999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3037</v>
+        <v>1.2622</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1665</v>
+        <v>-1.097</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5504</v>
+        <v>-0.5121</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6162</v>
+        <v>-0.585</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2321</v>
+        <v>0.2338</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3925</v>
+        <v>-1.4026</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6245</v>
+        <v>1.6364</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7706</v>
+        <v>1.784</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6667</v>
+        <v>1.6886</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1039</v>
+        <v>0.0954</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6772</v>
+        <v>0.6675</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2827</v>
+        <v>0.2701</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3945</v>
+        <v>0.3974</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3557</v>
+        <v>1.3553</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8373999999999997</v>
+        <v>0.7187999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5183</v>
+        <v>0.6365000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0181</v>
+        <v>4.0285</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3238</v>
+        <v>-1.3006</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3419</v>
+        <v>5.3291</v>
       </c>
       <c r="J5" t="n">
-        <v>4.1798</v>
+        <v>4.0847</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.5759</v>
+        <v>-1.609</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7557</v>
+        <v>5.6936</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1617</v>
+        <v>-0.05619999999999997</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2521</v>
+        <v>0.3084</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4137999999999999</v>
+        <v>-0.3644</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6245</v>
+        <v>-1.6363</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9452</v>
+        <v>-3.974</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3207</v>
+        <v>2.3377</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1076</v>
+        <v>-0.1069</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.07440000000000002</v>
+        <v>-0.05929999999999991</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.03320000000000001</v>
+        <v>-0.0476</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9304000000000001</v>
+        <v>-0.9298</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6772</v>
+        <v>0.6675</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6076</v>
+        <v>-1.5974</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2042000000000002</v>
+        <v>-0.1911</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8970000000000002</v>
+        <v>-0.9397999999999997</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6928</v>
+        <v>0.7487</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2562</v>
+        <v>-0.2601</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0591</v>
+        <v>-2.0546</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8029</v>
+        <v>1.7945</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2581</v>
+        <v>-0.3048</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.3484</v>
+        <v>-2.3737</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0903</v>
+        <v>2.0688</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001900000000000013</v>
+        <v>0.04480000000000003</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2893</v>
+        <v>0.3191</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2874</v>
+        <v>-0.2743</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4641000000000001</v>
+        <v>0.4675</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1604</v>
+        <v>-1.1688</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6245</v>
+        <v>1.6364</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6595</v>
+        <v>0.6663</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5214</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1381</v>
+        <v>0.1325</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0717</v>
+        <v>-1.0649</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0717</v>
+        <v>-1.0649</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5020000000000002</v>
+        <v>-0.5110999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7756000000000003</v>
+        <v>-0.8979999999999997</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2736</v>
+        <v>0.3869</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7672</v>
+        <v>1.7665</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.6869</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4743</v>
+        <v>2.4535</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0187</v>
+        <v>1.9173</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7866000000000001</v>
+        <v>-0.8277</v>
       </c>
       <c r="L7" t="n">
-        <v>2.8053</v>
+        <v>2.745</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2515</v>
+        <v>-0.1508</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0795</v>
+        <v>0.1408</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3310999999999999</v>
+        <v>-0.2916</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0887</v>
+        <v>-2.1039</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.9452</v>
+        <v>-3.9741</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8566</v>
+        <v>1.8702</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7499</v>
+        <v>0.7561</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4737000000000001</v>
+        <v>0.4912</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2761</v>
+        <v>0.2649</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9304</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6772</v>
+        <v>0.6676</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.6076</v>
+        <v>-1.5974</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.605</v>
+        <v>-0.5909</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5523</v>
+        <v>2.4462</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1573</v>
+        <v>-3.037</v>
       </c>
       <c r="G8" t="n">
-        <v>1.308</v>
+        <v>1.2911</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4116</v>
+        <v>1.4202</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1034999999999999</v>
+        <v>-0.1292</v>
       </c>
       <c r="J8" t="n">
-        <v>1.509</v>
+        <v>1.4028</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3228</v>
+        <v>1.2768</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1860999999999999</v>
+        <v>0.126</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2008</v>
+        <v>-0.1117</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0888</v>
+        <v>0.1434</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2897</v>
+        <v>-0.2551</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6962</v>
+        <v>0.7013</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3925</v>
+        <v>-1.4026</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0887</v>
+        <v>2.1039</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6059</v>
+        <v>0.6116</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8281999999999999</v>
+        <v>0.8486</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2224</v>
+        <v>-0.2371</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.215100000000001</v>
+        <v>-3.1948</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6076</v>
+        <v>1.5974</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.8227</v>
+        <v>-4.7922</v>
       </c>
     </row>
     <row r="9">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0758</v>
+        <v>-1.0709</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8338</v>
+        <v>-0.839</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.242</v>
+        <v>-0.2318</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9983</v>
+        <v>-0.9947</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1615</v>
+        <v>-1.1596</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1633</v>
+        <v>0.1649</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8164</v>
+        <v>-0.8245</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8164</v>
+        <v>-0.8245</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1819</v>
+        <v>-0.1703</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3452</v>
+        <v>-0.3352</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1633</v>
+        <v>0.1649</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0775</v>
+        <v>-0.0762</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0174</v>
+        <v>-0.0146</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0601</v>
+        <v>-0.0616</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6576</v>
+        <v>-2.6374</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.3303</v>
+        <v>-5.4229</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6728</v>
+        <v>2.7856</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.7228</v>
+        <v>-4.728899999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7444</v>
+        <v>-0.6977</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.9784</v>
+        <v>-4.0312</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.3814</v>
+        <v>-4.4833</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1614</v>
+        <v>-0.1761</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.2199</v>
+        <v>-4.3072</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3413</v>
+        <v>-0.2455</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5829</v>
+        <v>-0.5215000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2415</v>
+        <v>0.276</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7849</v>
+        <v>2.8052</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7849</v>
+        <v>2.8052</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5784</v>
+        <v>-0.5786</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9490000000000001</v>
+        <v>-0.9396</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3706</v>
+        <v>0.3609</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1413</v>
+        <v>-0.1351</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1413</v>
+        <v>-0.1351</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.914</v>
+        <v>-5.947900000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.6582</v>
+        <v>-6.8391</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7441999999999999</v>
+        <v>0.8913</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.2567</v>
+        <v>-6.271199999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.9548</v>
+        <v>-3.9443</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3019</v>
+        <v>-2.3269</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.8659</v>
+        <v>-4.0162</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.3457</v>
+        <v>-2.42</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5202</v>
+        <v>-1.5961</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3908</v>
+        <v>-2.255</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6091</v>
+        <v>-1.5243</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7817</v>
+        <v>-0.7307000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2321</v>
+        <v>-0.2337</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4811</v>
+        <v>-3.5065</v>
       </c>
       <c r="R11" t="n">
-        <v>3.249</v>
+        <v>3.2728</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6382</v>
+        <v>-0.6429</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6656</v>
+        <v>-0.6515</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02740000000000001</v>
+        <v>0.008599999999999997</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2131</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3544</v>
+        <v>1.3351</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1413</v>
+        <v>-0.1351</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.276399999999999</v>
+        <v>-9.3223</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.512700000000001</v>
+        <v>-8.6785</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7638</v>
+        <v>-0.6437</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.013400000000001</v>
+        <v>-5.0233</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.893</v>
+        <v>-2.8605</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1204</v>
+        <v>-2.1627</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.3834</v>
+        <v>-2.5127</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6355</v>
+        <v>-0.678</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.7479</v>
+        <v>-1.8347</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.63</v>
+        <v>-2.5105</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.2575</v>
+        <v>-2.1825</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3724999999999999</v>
+        <v>-0.328</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.4811</v>
+        <v>-3.5065</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.8018</v>
+        <v>-5.8441</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3208</v>
+        <v>2.3376</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5287999999999999</v>
+        <v>-0.5302</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0743</v>
+        <v>-0.05930000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4544</v>
+        <v>-0.4708</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2532</v>
+        <v>-0.2623</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2532</v>
+        <v>-0.2623</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.912100000000001</v>
+        <v>-9.9397</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.092599999999999</v>
+        <v>-9.2933</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8195000000000001</v>
+        <v>-0.6464000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.588100000000001</v>
+        <v>-6.6054</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.7852</v>
+        <v>-4.7728</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8029</v>
+        <v>-1.8326</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.3402</v>
+        <v>-5.5047</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.6659</v>
+        <v>-3.7432</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.6743</v>
+        <v>-1.7614</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2479</v>
+        <v>-1.1007</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1193</v>
+        <v>-1.0296</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1286</v>
+        <v>-0.0711</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.5528</v>
+        <v>-2.5714</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.1055</v>
+        <v>-5.1429</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5528</v>
+        <v>2.5714</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8831</v>
+        <v>-0.8902000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7904</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.1146</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1118</v>
+        <v>0.1273</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1434</v>
+        <v>2.1298</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.0316</v>
+        <v>-2.0026</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.2295</v>
+        <v>-18.2253</v>
       </c>
       <c r="E14" t="n">
-        <v>-23.492</v>
+        <v>-24.7764</v>
       </c>
       <c r="F14" t="n">
-        <v>5.262500000000001</v>
+        <v>6.551500000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.712</v>
+        <v>-14.6989</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.3207</v>
+        <v>-14.1431</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3912000000000002</v>
+        <v>-0.5556000000000016</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.2258</v>
+        <v>-5.345400000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.558699999999999</v>
+        <v>-8.0703</v>
       </c>
       <c r="L14" t="n">
-        <v>3.332700000000002</v>
+        <v>2.7249</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.4859</v>
+        <v>-9.353399999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.762</v>
+        <v>-6.073</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.7243</v>
+        <v>-3.2802</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.122599999999998</v>
+        <v>-8.1816</v>
       </c>
       <c r="Q14" t="n">
-        <v>-33.6505</v>
+        <v>-33.8961</v>
       </c>
       <c r="R14" t="n">
-        <v>25.528</v>
+        <v>25.7145</v>
       </c>
       <c r="S14" t="n">
-        <v>4.210199999999999</v>
+        <v>4.258000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>3.466600000000001</v>
+        <v>3.6649</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7436000000000001</v>
+        <v>0.5929</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3945000000000003</v>
+        <v>0.3974000000000011</v>
       </c>
       <c r="W14" t="n">
-        <v>10.9175</v>
+        <v>10.8</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.5229</v>
+        <v>-10.4026</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2079</v>
+        <v>5.1959</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5813999999999999</v>
+        <v>0.5485000000000002</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6265</v>
+        <v>4.6474</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3057</v>
+        <v>3.2945</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5234</v>
+        <v>3.5177</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2177</v>
+        <v>-0.2232</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6481</v>
+        <v>3.6466</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0622</v>
+        <v>3.0609</v>
       </c>
       <c r="L2" t="n">
-        <v>0.586</v>
+        <v>0.5856</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3425</v>
+        <v>-0.3521</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4611</v>
+        <v>0.4568</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8036</v>
+        <v>-0.8089</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.4415</v>
+        <v>-4.445</v>
       </c>
       <c r="Q2" t="n">
-        <v>-7.480499999999999</v>
+        <v>-7.4864</v>
       </c>
       <c r="R2" t="n">
-        <v>3.039</v>
+        <v>3.0413</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9567</v>
+        <v>1.9608</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6163</v>
+        <v>1.5934</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3404</v>
+        <v>0.3674</v>
       </c>
       <c r="V2" t="n">
-        <v>4.387</v>
+        <v>4.3857</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7974</v>
+        <v>2.7949</v>
       </c>
       <c r="X2" t="n">
-        <v>1.5896</v>
+        <v>1.5909</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3834</v>
+        <v>3.3795</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3805</v>
+        <v>3.368</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002800000000000025</v>
+        <v>0.01139999999999997</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5611999999999999</v>
+        <v>-0.5613999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2866</v>
+        <v>-0.2867999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2746</v>
+        <v>-0.2746999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7966999999999997</v>
+        <v>0.7987999999999997</v>
       </c>
       <c r="K3" t="n">
-        <v>1.054</v>
+        <v>1.0535</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2573000000000001</v>
+        <v>-0.2546999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.358</v>
+        <v>-1.3602</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3406</v>
+        <v>-1.3403</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0173</v>
+        <v>-0.0199</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1039</v>
+        <v>2.1055</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1039</v>
+        <v>2.1055</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3083</v>
+        <v>1.3033</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9863999999999999</v>
+        <v>0.9729000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3219</v>
+        <v>0.3303</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5324</v>
+        <v>0.5321</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5974</v>
+        <v>1.5963</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0649</v>
+        <v>-1.0642</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0394</v>
+        <v>2.0419</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0073</v>
+        <v>1.0017</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0321</v>
+        <v>1.0402</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6459000000000001</v>
+        <v>-0.6434</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3231</v>
+        <v>-1.321</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6772999999999999</v>
+        <v>0.6775999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4511999999999998</v>
+        <v>0.4571000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8110999999999999</v>
+        <v>-0.8080999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2622</v>
+        <v>1.2651</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.097</v>
+        <v>-1.1004</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5121</v>
+        <v>-0.5129999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.585</v>
+        <v>-0.5875</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2338</v>
+        <v>0.2339</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.4026</v>
+        <v>-1.4036</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6364</v>
+        <v>1.6376</v>
       </c>
       <c r="S4" t="n">
-        <v>1.784</v>
+        <v>1.7848</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6886</v>
+        <v>1.6796</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0954</v>
+        <v>0.1052</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6675</v>
+        <v>0.6665</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2701</v>
+        <v>0.2688</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3974</v>
+        <v>0.3977</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3553</v>
+        <v>1.3498</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7187999999999999</v>
+        <v>0.7027999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6365000000000001</v>
+        <v>0.6467999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0285</v>
+        <v>4.025700000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3006</v>
+        <v>-1.2997</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3291</v>
+        <v>5.3253</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0847</v>
+        <v>4.0892</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.609</v>
+        <v>-1.6052</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6936</v>
+        <v>5.6944</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.05619999999999997</v>
+        <v>-0.0635</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3084</v>
+        <v>0.3055</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3644</v>
+        <v>-0.3691</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6363</v>
+        <v>-1.6377</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.974</v>
+        <v>-3.9771</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3377</v>
+        <v>2.3394</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1069</v>
+        <v>-0.1085</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.05929999999999991</v>
+        <v>-0.07579999999999998</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0476</v>
+        <v>-0.0328</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9298</v>
+        <v>-0.9298000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6675</v>
+        <v>0.6665</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5974</v>
+        <v>-1.5963</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1911</v>
+        <v>-0.1896</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9397999999999997</v>
+        <v>-0.9446000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7487</v>
+        <v>0.755</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2601</v>
+        <v>-0.258</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0546</v>
+        <v>-2.0517</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7945</v>
+        <v>1.7936</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3048</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.3737</v>
+        <v>-2.369</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0688</v>
+        <v>2.0689</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04480000000000003</v>
+        <v>0.0421</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3191</v>
+        <v>0.3173</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2743</v>
+        <v>-0.2753</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4675</v>
+        <v>0.4679</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1688</v>
+        <v>-1.1697</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6364</v>
+        <v>1.6376</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6663</v>
+        <v>0.6647</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.5253</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1325</v>
+        <v>0.1395</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0649</v>
+        <v>-1.0642</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0649</v>
+        <v>-1.0642</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5110999999999999</v>
+        <v>-0.5129999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8979999999999997</v>
+        <v>-0.9100999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3869</v>
+        <v>0.3971</v>
       </c>
       <c r="G7" t="n">
         <v>1.7665</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6869</v>
+        <v>-0.6867</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4535</v>
+        <v>2.4531</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9173</v>
+        <v>1.9237</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8277</v>
+        <v>-0.8247</v>
       </c>
       <c r="L7" t="n">
-        <v>2.745</v>
+        <v>2.7484</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1508</v>
+        <v>-0.1573</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1408</v>
+        <v>0.138</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2916</v>
+        <v>-0.2953</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1039</v>
+        <v>-2.1056</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.9741</v>
+        <v>-3.9771</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8702</v>
+        <v>1.8716</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7561</v>
+        <v>0.7559</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4912</v>
+        <v>0.4768</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2649</v>
+        <v>0.279</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.9298</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6676</v>
+        <v>0.6665</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5974</v>
+        <v>-1.5963</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5909</v>
+        <v>-0.5889</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4462</v>
+        <v>2.4355</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.037</v>
+        <v>-3.0244</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2911</v>
+        <v>1.2913</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4202</v>
+        <v>1.4177</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1292</v>
+        <v>-0.1264000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4028</v>
+        <v>1.4087</v>
       </c>
       <c r="K8" t="n">
         <v>1.2768</v>
       </c>
       <c r="L8" t="n">
-        <v>0.126</v>
+        <v>0.1319</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1117</v>
+        <v>-0.1174</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1434</v>
+        <v>0.1409</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2551</v>
+        <v>-0.2583</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7013</v>
+        <v>0.7019</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.4026</v>
+        <v>-1.4036</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1039</v>
+        <v>2.1055</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6116</v>
+        <v>0.6107</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8486</v>
+        <v>0.8342999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2371</v>
+        <v>-0.2236</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.1948</v>
+        <v>-3.1926</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5974</v>
+        <v>1.5963</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.7922</v>
+        <v>-4.7889</v>
       </c>
     </row>
     <row r="9">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0709</v>
+        <v>-1.0716</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.839</v>
+        <v>-0.8406</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2318</v>
+        <v>-0.231</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9947</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1596</v>
+        <v>-1.1579</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1649</v>
+        <v>0.1646</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8245</v>
+        <v>-0.8229</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8245</v>
+        <v>-0.8229</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1703</v>
+        <v>-0.1705</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3352</v>
+        <v>-0.3351</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1649</v>
+        <v>0.1646</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0762</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0146</v>
+        <v>-0.0177</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0616</v>
+        <v>-0.0605</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6374</v>
+        <v>-2.6309</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4229</v>
+        <v>-5.4271</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7856</v>
+        <v>2.7962</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.728899999999999</v>
+        <v>-4.7207</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6977</v>
+        <v>-0.6985</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.0312</v>
+        <v>-4.022</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.4833</v>
+        <v>-4.4696</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1761</v>
+        <v>-0.1753</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.3072</v>
+        <v>-4.2944</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2455</v>
+        <v>-0.251</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5215000000000001</v>
+        <v>-0.5232</v>
       </c>
       <c r="O10" t="n">
-        <v>0.276</v>
+        <v>0.2723</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8052</v>
+        <v>2.8073</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8052</v>
+        <v>2.8073</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5786</v>
+        <v>-0.5832999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9396</v>
+        <v>-0.9574</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3609</v>
+        <v>0.3743</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1351</v>
+        <v>-0.1344</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1351</v>
+        <v>-0.1344</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.947900000000001</v>
+        <v>-5.9396</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.8391</v>
+        <v>-6.8484</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8913</v>
+        <v>0.9087999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.271199999999999</v>
+        <v>-6.2609</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.9443</v>
+        <v>-3.9387</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3269</v>
+        <v>-2.3222</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.0162</v>
+        <v>-4.0003</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.42</v>
+        <v>-2.4132</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5961</v>
+        <v>-1.5871</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.255</v>
+        <v>-2.2606</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5243</v>
+        <v>-1.5255</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7307000000000001</v>
+        <v>-0.7351000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2337</v>
+        <v>-0.234</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.5065</v>
+        <v>-3.5092</v>
       </c>
       <c r="R11" t="n">
-        <v>3.2728</v>
+        <v>3.2752</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6429</v>
+        <v>-0.6434</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6515</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.008599999999999997</v>
+        <v>0.02859999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.1986</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3351</v>
+        <v>1.333</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1351</v>
+        <v>-0.1344</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.3223</v>
+        <v>-9.319800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.6785</v>
+        <v>-8.6873</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6437</v>
+        <v>-0.6324</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.0233</v>
+        <v>-5.0139</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.8605</v>
+        <v>-2.8576</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1627</v>
+        <v>-2.1564</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5127</v>
+        <v>-2.4995</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.678</v>
+        <v>-0.6752</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8347</v>
+        <v>-1.8243</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5105</v>
+        <v>-2.5145</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.1825</v>
+        <v>-2.1823</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.328</v>
+        <v>-0.3322000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.5065</v>
+        <v>-3.5092</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.8441</v>
+        <v>-5.8487</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3376</v>
+        <v>2.3394</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5302</v>
+        <v>-0.5332</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.05930000000000001</v>
+        <v>-0.07579999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4708</v>
+        <v>-0.4574999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2623</v>
+        <v>-0.2633</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2623</v>
+        <v>-0.2633</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.9397</v>
+        <v>-9.928599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.2933</v>
+        <v>-9.301500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6464000000000001</v>
+        <v>-0.6271</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.6054</v>
+        <v>-6.5939</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.7728</v>
+        <v>-4.766</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8326</v>
+        <v>-1.8279</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.5047</v>
+        <v>-5.485300000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.7432</v>
+        <v>-3.7342</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.7614</v>
+        <v>-1.7511</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1007</v>
+        <v>-1.1086</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0296</v>
+        <v>-1.0318</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0711</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.5714</v>
+        <v>-2.5734</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.1429</v>
+        <v>-5.1469</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5714</v>
+        <v>2.5734</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8902000000000001</v>
+        <v>-0.8901999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.7978000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1146</v>
+        <v>-0.09250000000000003</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1273</v>
+        <v>0.1289</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1298</v>
+        <v>2.1284</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.0026</v>
+        <v>-1.9995</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.2253</v>
+        <v>-18.2149</v>
       </c>
       <c r="E14" t="n">
-        <v>-24.7764</v>
+        <v>-24.9031</v>
       </c>
       <c r="F14" t="n">
-        <v>6.551500000000001</v>
+        <v>6.688000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.6989</v>
+        <v>-14.6676</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.1431</v>
+        <v>-14.1292</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5556000000000016</v>
+        <v>-0.5385999999999993</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.345400000000001</v>
+        <v>-5.253499999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-8.0703</v>
+        <v>-8.0366</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7249</v>
+        <v>2.782699999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.353399999999999</v>
+        <v>-9.414000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.073</v>
+        <v>-6.092700000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.2802</v>
+        <v>-3.3215</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.1816</v>
+        <v>-8.1884</v>
       </c>
       <c r="Q14" t="n">
-        <v>-33.8961</v>
+        <v>-33.9223</v>
       </c>
       <c r="R14" t="n">
-        <v>25.7145</v>
+        <v>25.7338</v>
       </c>
       <c r="S14" t="n">
-        <v>4.258000000000001</v>
+        <v>4.2434</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6649</v>
+        <v>3.4859</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5929</v>
+        <v>0.7574</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3974000000000011</v>
+        <v>0.3976999999999993</v>
       </c>
       <c r="W14" t="n">
-        <v>10.8</v>
+        <v>10.7874</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.4026</v>
+        <v>-10.3896</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/aggregate_individual/AGG_IND_Surne Bilbao Basket.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,122 +417,122 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>GP</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Total_NP</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Off_NP</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Def_NP</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Net_Shooting</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Net_2P</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Net_3P</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Off_Shooting</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Off_2P</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Off_3P</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Def_Shooting</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Def_2P</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Def_3P</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Net_TOV</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Off_TOV</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Def_TOV</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Net_ORB</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Off_ORB</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Def_ORB</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Net_FT</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Off_FT</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Def_FT</t>
         </is>
@@ -565,67 +553,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1959</v>
+        <v>5.1932</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5485000000000002</v>
+        <v>0.5436999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6474</v>
+        <v>4.6494</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2945</v>
+        <v>3.2914</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5177</v>
+        <v>3.5164</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2232</v>
+        <v>-0.225</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6466</v>
+        <v>3.6473</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0609</v>
+        <v>3.0617</v>
       </c>
       <c r="L2" t="n">
         <v>0.5856</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3521</v>
+        <v>-0.3559</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4568</v>
+        <v>0.4548</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8089</v>
+        <v>-0.8107</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.445</v>
+        <v>-4.4453</v>
       </c>
       <c r="Q2" t="n">
-        <v>-7.4864</v>
+        <v>-7.486800000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0413</v>
+        <v>3.0416</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9608</v>
+        <v>1.9614</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5934</v>
+        <v>1.5886</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3674</v>
+        <v>0.3728</v>
       </c>
       <c r="V2" t="n">
         <v>4.3857</v>
       </c>
       <c r="W2" t="n">
-        <v>2.7949</v>
+        <v>2.7947</v>
       </c>
       <c r="X2" t="n">
-        <v>1.5909</v>
+        <v>1.591</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +631,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3795</v>
+        <v>3.3782</v>
       </c>
       <c r="E3" t="n">
-        <v>3.368</v>
+        <v>3.3662</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01139999999999997</v>
+        <v>0.0121</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5613999999999999</v>
+        <v>-0.5616999999999996</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.2867999999999999</v>
+        <v>-0.2868999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2746999999999999</v>
+        <v>-0.2747000000000002</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7987999999999997</v>
+        <v>0.7997999999999998</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0535</v>
+        <v>1.0538</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2546999999999999</v>
+        <v>-0.254</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3602</v>
+        <v>-1.3614</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3403</v>
+        <v>-1.3406</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0199</v>
+        <v>-0.0208</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1055</v>
+        <v>2.1056</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1055</v>
+        <v>2.1056</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3033</v>
+        <v>1.3022</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9729000000000001</v>
+        <v>0.9702</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3303</v>
+        <v>0.332</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5321</v>
+        <v>0.532</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5963</v>
+        <v>1.5962</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0642</v>
+        <v>-1.0641</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +709,64 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0419</v>
+        <v>2.0426</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0017</v>
+        <v>1.0018</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0402</v>
+        <v>1.0408</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6434</v>
+        <v>-0.6427999999999998</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.321</v>
+        <v>-1.3205</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6775999999999999</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4571000000000001</v>
+        <v>0.4592000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8080999999999999</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2651</v>
+        <v>1.2662</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1004</v>
+        <v>-1.102</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5129999999999999</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5875</v>
+        <v>-0.5884</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2339</v>
+        <v>0.234</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.4036</v>
+        <v>-1.4038</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6376</v>
+        <v>1.6378</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7848</v>
+        <v>1.7849</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6796</v>
+        <v>1.6776</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1052</v>
+        <v>0.1073</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6665</v>
+        <v>0.6664</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2688</v>
+        <v>0.2687</v>
       </c>
       <c r="X4" t="n">
         <v>0.3977</v>
@@ -799,67 +787,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3498</v>
+        <v>1.3487</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7027999999999999</v>
+        <v>0.7012</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6467999999999999</v>
+        <v>0.6475000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>4.025700000000001</v>
+        <v>4.024999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2997</v>
+        <v>-1.2998</v>
       </c>
       <c r="I5" t="n">
-        <v>5.3253</v>
+        <v>5.3247</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0892</v>
+        <v>4.0913</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.6052</v>
+        <v>-1.604</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6944</v>
+        <v>5.6953</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0635</v>
+        <v>-0.06629999999999997</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3055</v>
+        <v>0.3042</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3691</v>
+        <v>-0.3706</v>
       </c>
       <c r="P5" t="n">
         <v>-1.6377</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9771</v>
+        <v>-3.9774</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3394</v>
+        <v>2.3396</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1085</v>
+        <v>-0.1089</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.07579999999999998</v>
+        <v>-0.07910000000000006</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0328</v>
+        <v>-0.02960000000000002</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9298000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6665</v>
+        <v>0.6664</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5963</v>
+        <v>-1.5962</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +865,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1896</v>
+        <v>-0.1894</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9446000000000001</v>
+        <v>-0.9450000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.755</v>
+        <v>0.7555999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.258</v>
+        <v>-0.2575000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0517</v>
+        <v>-2.0511</v>
       </c>
       <c r="I6" t="n">
         <v>1.7936</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2999999999999998</v>
+        <v>-0.2985</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.369</v>
+        <v>-2.3677</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0689</v>
+        <v>2.0692</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0421</v>
+        <v>0.04100000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3173</v>
+        <v>0.3167</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2753</v>
+        <v>-0.2757</v>
       </c>
       <c r="P6" t="n">
         <v>0.4679</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1697</v>
+        <v>-1.1698</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6376</v>
+        <v>1.6378</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6647</v>
+        <v>0.6644</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5253</v>
+        <v>0.5233</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1395</v>
+        <v>0.1409</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0642</v>
+        <v>-1.0641</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0642</v>
+        <v>-1.0641</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +943,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5129999999999999</v>
+        <v>-0.5133000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9100999999999999</v>
+        <v>-0.9109000000000003</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3971</v>
+        <v>0.3977</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7665</v>
+        <v>1.7664</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6867</v>
+        <v>-0.6869</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4531</v>
+        <v>2.4533</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9237</v>
+        <v>1.9262</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8247</v>
+        <v>-0.8236</v>
       </c>
       <c r="L7" t="n">
-        <v>2.7484</v>
+        <v>2.7498</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1573</v>
+        <v>-0.1598</v>
       </c>
       <c r="N7" t="n">
-        <v>0.138</v>
+        <v>0.1366</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2953</v>
+        <v>-0.2965</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1056</v>
+        <v>-2.1057</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.9771</v>
+        <v>-3.9774</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8716</v>
+        <v>1.8718</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7559</v>
+        <v>0.7558</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4768</v>
+        <v>0.4739</v>
       </c>
       <c r="U7" t="n">
-        <v>0.279</v>
+        <v>0.2819</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9298</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6665</v>
+        <v>0.6664</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5963</v>
+        <v>-1.5962</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1021,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5889</v>
+        <v>-0.5886</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4355</v>
+        <v>2.4348</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.0244</v>
+        <v>-3.0233</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2913</v>
+        <v>1.2915</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4177</v>
+        <v>1.4171</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1264000000000001</v>
+        <v>-0.1256</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4087</v>
+        <v>1.4111</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2768</v>
+        <v>1.2773</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1319</v>
+        <v>0.1337999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1174</v>
+        <v>-0.1196</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1409</v>
+        <v>0.1397</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2583</v>
+        <v>-0.2594</v>
       </c>
       <c r="P8" t="n">
         <v>0.7019</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.4036</v>
+        <v>-1.4038</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1055</v>
+        <v>2.1057</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6107</v>
+        <v>0.6103999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8342999999999999</v>
+        <v>0.8311999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2236</v>
+        <v>-0.2208</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.1926</v>
+        <v>-3.1924</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5963</v>
+        <v>1.5962</v>
       </c>
       <c r="X8" t="n">
-        <v>-4.7889</v>
+        <v>-4.7887</v>
       </c>
     </row>
     <row r="9">
@@ -1111,40 +1099,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0716</v>
+        <v>-1.0718</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8406</v>
+        <v>-0.8408</v>
       </c>
       <c r="F9" t="n">
         <v>-0.231</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.9931</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1579</v>
+        <v>-1.1576</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1646</v>
+        <v>0.1645</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8229</v>
+        <v>-0.8225</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8229</v>
+        <v>-0.8225</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1705</v>
+        <v>-0.1707</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3351</v>
+        <v>-0.3352</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1646</v>
+        <v>0.1645</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1144,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0177</v>
+        <v>-0.0184</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0605</v>
+        <v>-0.0603</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1177,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6309</v>
+        <v>-2.6298</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4271</v>
+        <v>-5.4268</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7962</v>
+        <v>2.797</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.7207</v>
+        <v>-4.719</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6985</v>
+        <v>-0.6993</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.022</v>
+        <v>-4.019600000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.4696</v>
+        <v>-4.4657</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1753</v>
+        <v>-0.1749</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.2944</v>
+        <v>-4.2908</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.251</v>
+        <v>-0.2533</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5232</v>
+        <v>-0.5244</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2723</v>
+        <v>0.2711</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8073</v>
+        <v>2.8075</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8073</v>
+        <v>2.8075</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5832999999999999</v>
+        <v>-0.5841000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9574</v>
+        <v>-0.9611</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3743</v>
+        <v>0.3769</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1344</v>
+        <v>-0.1343</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1344</v>
+        <v>-0.1343</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1255,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9396</v>
+        <v>-5.9376</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.8484</v>
+        <v>-6.848</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9087999999999999</v>
+        <v>0.9104000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.2609</v>
+        <v>-6.2587</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.9387</v>
+        <v>-3.9377</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3222</v>
+        <v>-2.3209</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.0003</v>
+        <v>-3.9953</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.4132</v>
+        <v>-2.411</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5871</v>
+        <v>-1.5844</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2606</v>
+        <v>-2.2634</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5255</v>
+        <v>-1.5268</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7351000000000001</v>
+        <v>-0.7366</v>
       </c>
       <c r="P11" t="n">
         <v>-0.234</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.5092</v>
+        <v>-3.5094</v>
       </c>
       <c r="R11" t="n">
-        <v>3.2752</v>
+        <v>3.2754</v>
       </c>
       <c r="S11" t="n">
         <v>-0.6434</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.676</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02859999999999999</v>
+        <v>0.03259999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1986</v>
+        <v>1.1985</v>
       </c>
       <c r="W11" t="n">
-        <v>1.333</v>
+        <v>1.3328</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1344</v>
+        <v>-0.1343</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1333,64 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.319800000000001</v>
+        <v>-9.3187</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.6873</v>
+        <v>-8.6869</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6324</v>
+        <v>-0.6317</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.0139</v>
+        <v>-5.012</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.8576</v>
+        <v>-2.8573</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1564</v>
+        <v>-2.1547</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4995</v>
+        <v>-2.4953</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6752</v>
+        <v>-0.6742</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8243</v>
+        <v>-1.8212</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5145</v>
+        <v>-2.5167</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.1823</v>
+        <v>-2.1832</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3322000000000001</v>
+        <v>-0.3335</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.5092</v>
+        <v>-3.5094</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.8487</v>
+        <v>-5.8491</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3394</v>
+        <v>2.3396</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5332</v>
+        <v>-0.5339</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.07579999999999999</v>
+        <v>-0.0791</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4574999999999999</v>
+        <v>-0.4547</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2633</v>
+        <v>-0.2634</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2633</v>
+        <v>-0.2634</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1411,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.928599999999999</v>
+        <v>-9.9261</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.301500000000001</v>
+        <v>-9.300599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6271</v>
+        <v>-0.6255000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.5939</v>
+        <v>-6.5914</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.766</v>
+        <v>-4.7648</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8279</v>
+        <v>-1.8266</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.485300000000001</v>
+        <v>-5.4795</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.7342</v>
+        <v>-3.7316</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.7511</v>
+        <v>-1.7479</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1086</v>
+        <v>-1.1119</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0318</v>
+        <v>-1.0334</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.07859999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.5734</v>
+        <v>-2.5736</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.1469</v>
+        <v>-5.1472</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5734</v>
+        <v>2.5736</v>
       </c>
       <c r="S13" t="n">
         <v>-0.8901999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7978000000000001</v>
+        <v>-0.8021999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09250000000000003</v>
+        <v>-0.08789999999999998</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1289</v>
+        <v>0.129</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1284</v>
+        <v>2.1282</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.9995</v>
+        <v>-1.9992</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1489,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.2149</v>
+        <v>-18.21259999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-24.9031</v>
+        <v>-24.9113</v>
       </c>
       <c r="F14" t="n">
-        <v>6.688000000000001</v>
+        <v>6.699000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.6676</v>
+        <v>-14.6619</v>
       </c>
       <c r="H14" t="n">
-        <v>-14.1292</v>
+        <v>-14.1284</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5385999999999993</v>
+        <v>-0.5331000000000019</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.253499999999999</v>
+        <v>-5.221900000000003</v>
       </c>
       <c r="K14" t="n">
-        <v>-8.0366</v>
+        <v>-8.023700000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>2.782699999999998</v>
+        <v>2.801600000000003</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.414000000000001</v>
+        <v>-9.440000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.092700000000001</v>
+        <v>-6.105200000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.3215</v>
+        <v>-3.3352</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.1884</v>
+        <v>-8.188799999999997</v>
       </c>
       <c r="Q14" t="n">
-        <v>-33.9223</v>
+        <v>-33.9247</v>
       </c>
       <c r="R14" t="n">
-        <v>25.7338</v>
+        <v>25.736</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2434</v>
+        <v>4.239899999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.4859</v>
+        <v>3.448899999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7574</v>
+        <v>0.7910999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3976999999999993</v>
+        <v>0.3977999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>10.7874</v>
+        <v>10.7862</v>
       </c>
       <c r="X14" t="n">
-        <v>-10.3896</v>
+        <v>-10.3884</v>
       </c>
     </row>
   </sheetData>
